--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484369_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484369_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6026</v>
+        <v>6.4679</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8075</v>
+        <v>5.8362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7951</v>
+        <v>0.6317</v>
       </c>
       <c r="G2" t="n">
         <v>5.1115</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>1.718</v>
+        <v>0.5833</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7226</v>
+        <v>0.7513</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0046</v>
+        <v>-0.168</v>
       </c>
       <c r="V2" t="n">
         <v>1.1638</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4358</v>
+        <v>2.2959</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4437</v>
+        <v>1.1403</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9921</v>
+        <v>1.1555</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1094</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.8193</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3895</v>
+        <v>1.0862</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4303</v>
+        <v>-0.2669</v>
       </c>
       <c r="V3" t="n">
         <v>1.2186</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7515</v>
+        <v>1.4015</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4548</v>
+        <v>1.0504</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2966</v>
+        <v>0.3511</v>
       </c>
       <c r="G4" t="n">
         <v>1.506</v>
@@ -766,13 +766,13 @@
         <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0501</v>
+        <v>-0.2999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5531</v>
+        <v>0.1486</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.503</v>
+        <v>-0.4485</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2298</v>
+        <v>0.0178</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0833</v>
+        <v>-0.6995</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8535</v>
+        <v>0.7173</v>
       </c>
       <c r="G5" t="n">
         <v>1.0604</v>
@@ -844,13 +844,13 @@
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0483</v>
+        <v>-0.8007</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4291</v>
+        <v>-0.0453</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6192</v>
+        <v>-0.7554</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2186</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7379</v>
+        <v>-1.7691</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.463</v>
+        <v>-2.5246</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2749</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8874</v>
+        <v>-3.3237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0435</v>
+        <v>-2.3257</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.998</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3879</v>
+        <v>-2.0104</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2724</v>
+        <v>-1.283</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6603</v>
+        <v>-0.7274</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4996</v>
+        <v>-1.3133</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2289</v>
+        <v>-1.0427</v>
       </c>
       <c r="O6" t="n">
         <v>-0.2706</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3441</v>
+        <v>-1.3674</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1255</v>
+        <v>2.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5245</v>
+        <v>-0.2854</v>
       </c>
       <c r="T6" t="n">
-        <v>0.988</v>
+        <v>0.5759</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4635</v>
+        <v>-0.8613</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.1563</v>
+        <v>0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.719</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7405</v>
+        <v>-2.1878</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3667</v>
+        <v>-2.8412</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6262</v>
+        <v>0.6534</v>
       </c>
       <c r="G7" t="n">
         <v>-2.8215</v>
@@ -1000,13 +1000,13 @@
         <v>2.3441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.931</v>
+        <v>-0.3783</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0029</v>
+        <v>0.5284</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9339</v>
+        <v>-0.9067</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9414</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9479</v>
+        <v>-2.4635</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0608</v>
+        <v>-3.4947</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1129</v>
+        <v>1.0312</v>
       </c>
       <c r="G8" t="n">
         <v>-1.559</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2168</v>
+        <v>0.2676</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2283</v>
+        <v>0.3378</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0115</v>
+        <v>-0.0702</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0569</v>
+        <v>-2.7746</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.758</v>
+        <v>-3.0587</v>
       </c>
       <c r="F9" t="n">
-        <v>0.701</v>
+        <v>0.2841</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3237</v>
+        <v>-0.8606</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3257</v>
+        <v>2.4702</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.998</v>
+        <v>-3.3308</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0104</v>
+        <v>-1.0353</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.283</v>
+        <v>2.2947</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7274</v>
+        <v>-3.33</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3133</v>
+        <v>0.1747</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0427</v>
+        <v>0.1755</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2706</v>
+        <v>-0.0008</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3674</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9301</v>
+        <v>2.7348</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5732</v>
+        <v>-1.4768</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6574</v>
+        <v>-0.3472</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.1296</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
         <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.489</v>
+        <v>-3.7115</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7458</v>
+        <v>-3.1915</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2568</v>
+        <v>-0.52</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8606</v>
+        <v>-0.8874</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4702</v>
+        <v>0.0435</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3308</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0353</v>
+        <v>-0.3879</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2947</v>
+        <v>0.2724</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.33</v>
+        <v>-0.6603</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1747</v>
+        <v>-0.4996</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1755</v>
+        <v>-0.2289</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0008</v>
+        <v>-0.2706</v>
       </c>
       <c r="P10" t="n">
         <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-2.3441</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7348</v>
+        <v>3.1255</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1911</v>
+        <v>-0.4491</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0343</v>
+        <v>0.2595</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1568</v>
+        <v>-0.7086</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>-3.1563</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>-0.719</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4959</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.86</v>
+        <v>-7.3383</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.7798</v>
+        <v>-8.557600000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9197</v>
+        <v>1.2193</v>
       </c>
       <c r="G11" t="n">
         <v>-3.511</v>
@@ -1312,13 +1312,13 @@
         <v>2.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2941</v>
+        <v>-0.7724</v>
       </c>
       <c r="T11" t="n">
-        <v>0.212</v>
+        <v>0.4342</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5062</v>
+        <v>-1.2066</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8828</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.2721</v>
+        <v>-10.0617</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.5514</v>
+        <v>-16.3409</v>
       </c>
       <c r="F12" t="n">
-        <v>6.279</v>
+        <v>6.2791</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.394699999999999</v>
+        <v>-6.3947</v>
       </c>
       <c r="H12" t="n">
         <v>2.3714</v>
@@ -1363,16 +1363,16 @@
         <v>-8.7662</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.496200000000001</v>
+        <v>-6.4962</v>
       </c>
       <c r="K12" t="n">
-        <v>4.961500000000001</v>
+        <v>4.9615</v>
       </c>
       <c r="L12" t="n">
         <v>-11.4576</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1016000000000002</v>
+        <v>0.1016</v>
       </c>
       <c r="N12" t="n">
         <v>-2.5899</v>
@@ -1390,22 +1390,22 @@
         <v>20.5109</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.002700000000001</v>
+        <v>-2.7924</v>
       </c>
       <c r="T12" t="n">
-        <v>2.519</v>
+        <v>3.7294</v>
       </c>
       <c r="U12" t="n">
         <v>-6.521799999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.7581</v>
+        <v>-5.758100000000001</v>
       </c>
       <c r="W12" t="n">
         <v>2.0532</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.811399999999999</v>
+        <v>-7.811400000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0137</v>
+        <v>4.6717</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5769</v>
+        <v>2.588</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4368</v>
+        <v>2.0837</v>
       </c>
       <c r="G13" t="n">
         <v>3.1168</v>
@@ -1468,13 +1468,13 @@
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4352</v>
+        <v>0.2228</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.652</v>
+        <v>0.3592</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7833</v>
+        <v>-0.1364</v>
       </c>
       <c r="V13" t="n">
         <v>0.9414</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.985</v>
+        <v>3.9249</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0408</v>
+        <v>1.1419</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9441</v>
+        <v>2.783</v>
       </c>
       <c r="G14" t="n">
         <v>0.9335</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2273</v>
+        <v>1.1673</v>
       </c>
       <c r="T14" t="n">
-        <v>0.743</v>
+        <v>0.8441</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5157</v>
+        <v>0.3232</v>
       </c>
       <c r="V14" t="n">
         <v>2.2149</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0087</v>
+        <v>3.0096</v>
       </c>
       <c r="E15" t="n">
         <v>-1.0691</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0777</v>
+        <v>4.0787</v>
       </c>
       <c r="G15" t="n">
         <v>0.5741000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.548</v>
+        <v>1.549</v>
       </c>
       <c r="T15" t="n">
         <v>0.9329</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3848</v>
+        <v>0.6161</v>
       </c>
       <c r="V15" t="n">
         <v>0.8865</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8864</v>
+        <v>2.2014</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2559</v>
+        <v>0.3571</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6305</v>
+        <v>1.8443</v>
       </c>
       <c r="G16" t="n">
         <v>2.5022</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6735</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.245</v>
+        <v>0.3461</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4285</v>
+        <v>0.6423</v>
       </c>
       <c r="V16" t="n">
         <v>0.6642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5214</v>
+        <v>2.0579</v>
       </c>
       <c r="E17" t="n">
         <v>-2.3227</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8441</v>
+        <v>4.3807</v>
       </c>
       <c r="G17" t="n">
         <v>-3.0297</v>
@@ -1780,13 +1780,13 @@
         <v>2.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6562</v>
+        <v>2.1928</v>
       </c>
       <c r="T17" t="n">
         <v>1.3649</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2913</v>
+        <v>0.8279</v>
       </c>
       <c r="V17" t="n">
         <v>0.9414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3077</v>
+        <v>0.5321</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8183</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.1851</v>
       </c>
       <c r="G18" t="n">
         <v>0.7529</v>
@@ -1858,13 +1858,13 @@
         <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6405</v>
+        <v>-0.4161</v>
       </c>
       <c r="T18" t="n">
-        <v>0.311</v>
+        <v>0.2098</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9515</v>
+        <v>-0.626</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1593</v>
+        <v>-0.0439</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3865</v>
+        <v>-3.8921</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2272</v>
+        <v>3.8482</v>
       </c>
       <c r="G19" t="n">
         <v>2.6458</v>
@@ -1936,13 +1936,13 @@
         <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7148</v>
+        <v>0.8302</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4171</v>
+        <v>0.9115</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7023</v>
+        <v>-0.0813</v>
       </c>
       <c r="V19" t="n">
         <v>0.3869</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2914</v>
+        <v>-0.3629</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1929</v>
+        <v>-3.7996</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9015</v>
+        <v>3.4367</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1009</v>
@@ -2014,13 +2014,13 @@
         <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>2.2588</v>
+        <v>2.1873</v>
       </c>
       <c r="T20" t="n">
-        <v>2.16</v>
+        <v>1.5534</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0987</v>
+        <v>0.6339</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>11.2722</v>
+        <v>15.9908</v>
       </c>
       <c r="E21" t="n">
         <v>-6.2793</v>
       </c>
       <c r="F21" t="n">
-        <v>17.5513</v>
+        <v>22.2702</v>
       </c>
       <c r="G21" t="n">
         <v>6.394699999999999</v>
@@ -2092,13 +2092,13 @@
         <v>15.6275</v>
       </c>
       <c r="S21" t="n">
-        <v>4.002899999999999</v>
+        <v>8.7217</v>
       </c>
       <c r="T21" t="n">
         <v>6.5219</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.5191</v>
+        <v>2.1997</v>
       </c>
       <c r="V21" t="n">
         <v>5.7581</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484369_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484369_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +736,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4015</v>
+        <v>2.1419</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0504</v>
+        <v>2.1419</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3511</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.506</v>
+        <v>2.1419</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3712</v>
+        <v>1.5349</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1348</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9018</v>
+        <v>2.1419</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9018</v>
+        <v>1.5349</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6042999999999999</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4694</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2999</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1486</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4485</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -782,12 +797,17 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0178</v>
+        <v>1.4015</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6995</v>
+        <v>1.0504</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7173</v>
+        <v>0.3511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0604</v>
+        <v>1.506</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0604</v>
+        <v>1.3712</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0.1348</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2635</v>
+        <v>0.9018</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0847</v>
+        <v>0.9018</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3482</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3239</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0243</v>
+        <v>0.4694</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3482</v>
+        <v>0.1348</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8007</v>
+        <v>-0.2999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0453</v>
+        <v>0.1486</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7554</v>
+        <v>-0.4485</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7691</v>
+        <v>0.307</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5246</v>
+        <v>0.307</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7554999999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.3237</v>
+        <v>0.307</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3257</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.998</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.0104</v>
+        <v>0.307</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.283</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7274</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3133</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0427</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2706</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2854</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5759</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8613</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1878</v>
+        <v>0.0178</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8412</v>
+        <v>-0.6995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6534</v>
+        <v>0.7173</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.8215</v>
+        <v>1.0604</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1046</v>
+        <v>1.0604</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9262</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.592</v>
+        <v>-0.2635</v>
       </c>
       <c r="K7" t="n">
-        <v>0.738</v>
+        <v>1.0847</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.33</v>
+        <v>-1.3482</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2295</v>
+        <v>1.3239</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6334</v>
+        <v>-0.0243</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4039</v>
+        <v>1.3482</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.3907</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3783</v>
+        <v>-0.8007</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5284</v>
+        <v>-0.0453</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9067</v>
+        <v>-0.7554</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9414</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4635</v>
+        <v>-1.7691</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4947</v>
+        <v>-2.5246</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0312</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.559</v>
+        <v>-3.3237</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8849</v>
+        <v>-2.3257</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6741</v>
+        <v>-0.998</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.879</v>
+        <v>-2.0104</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5308</v>
+        <v>-1.283</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3482</v>
+        <v>-0.7274</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3201</v>
+        <v>-1.3133</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.354</v>
+        <v>-1.0427</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6741</v>
+        <v>-0.2706</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-1.3674</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>2.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2676</v>
+        <v>-0.2854</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3378</v>
+        <v>0.5759</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0702</v>
+        <v>-0.8613</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7746</v>
+        <v>-2.4635</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0587</v>
+        <v>-3.4947</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2841</v>
+        <v>1.0312</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8606</v>
+        <v>-1.559</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4702</v>
+        <v>-0.8849</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.3308</v>
+        <v>-0.6741</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0353</v>
+        <v>-1.879</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2947</v>
+        <v>-0.5308</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.33</v>
+        <v>-1.3482</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1747</v>
+        <v>0.3201</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1755</v>
+        <v>-0.354</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0008</v>
+        <v>0.6741</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7348</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4768</v>
+        <v>0.2676</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3472</v>
+        <v>0.3378</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1296</v>
+        <v>-0.0702</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7115</v>
+        <v>-2.4947</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1915</v>
+        <v>-3.1482</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.52</v>
+        <v>0.6534</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8874</v>
+        <v>-3.1285</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0435</v>
+        <v>-0.2023</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-2.9262</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3879</v>
+        <v>-2.899</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2724</v>
+        <v>0.431</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6603</v>
+        <v>-3.33</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4996</v>
+        <v>-0.2295</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2289</v>
+        <v>-0.6334</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2706</v>
+        <v>0.4039</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3441</v>
+        <v>-0.3907</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1255</v>
+        <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4491</v>
+        <v>-0.3783</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2595</v>
+        <v>0.5284</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7086</v>
+        <v>-0.9067</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1563</v>
+        <v>-0.9414</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.719</v>
+        <v>-0.3869</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3383</v>
+        <v>-2.7746</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.557600000000001</v>
+        <v>-3.0587</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2193</v>
+        <v>0.2841</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.511</v>
+        <v>-0.8606</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5288</v>
+        <v>2.4702</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9822</v>
+        <v>-3.3308</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.2254</v>
+        <v>-1.0353</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5695</v>
+        <v>2.2947</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.6559</v>
+        <v>-3.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7144</v>
+        <v>0.1747</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0407</v>
+        <v>0.1755</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6737</v>
+        <v>-0.0008</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1022</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9301</v>
+        <v>2.7348</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7724</v>
+        <v>-1.4768</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4342</v>
+        <v>-0.3472</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2066</v>
+        <v>-1.1296</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.0617</v>
+        <v>-5.8534</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.3409</v>
+        <v>-5.3334</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2791</v>
+        <v>-0.52</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.3947</v>
+        <v>-3.0294</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3714</v>
+        <v>-1.4915</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.7662</v>
+        <v>-1.5379</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.4962</v>
+        <v>-2.5298</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9615</v>
+        <v>-1.2625</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.4576</v>
+        <v>-1.2673</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1016</v>
+        <v>-0.4996</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.5899</v>
+        <v>-0.2289</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6915</v>
+        <v>-0.2706</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8834</v>
+        <v>0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.6274</v>
+        <v>-2.3441</v>
       </c>
       <c r="R12" t="n">
-        <v>20.5109</v>
+        <v>3.1255</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7924</v>
+        <v>-0.4491</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7294</v>
+        <v>0.2595</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.521799999999999</v>
+        <v>-0.7086</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.758100000000001</v>
+        <v>-3.1563</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0532</v>
+        <v>-0.719</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.811400000000001</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6717</v>
+        <v>-7.3383</v>
       </c>
       <c r="E13" t="n">
-        <v>2.588</v>
+        <v>-8.557600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0837</v>
+        <v>1.2193</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1168</v>
+        <v>-3.511</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4183</v>
+        <v>-1.5288</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6986</v>
+        <v>-1.9822</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6631</v>
+        <v>-4.2254</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5822</v>
+        <v>-1.5695</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0809</v>
+        <v>-2.6559</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4537</v>
+        <v>0.7144</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1639</v>
+        <v>0.0407</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6176</v>
+        <v>0.6737</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1488</v>
+        <v>-4.1022</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5395</v>
+        <v>2.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2228</v>
+        <v>-0.7724</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3592</v>
+        <v>0.4342</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1364</v>
+        <v>-1.2066</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9414</v>
+        <v>-1.8828</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7145</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7731</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9249</v>
+        <v>-10.0616</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1419</v>
+        <v>-16.3409</v>
       </c>
       <c r="F14" t="n">
-        <v>2.783</v>
+        <v>6.279100000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9335</v>
+        <v>-6.394799999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8442</v>
+        <v>2.3714</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7777</v>
+        <v>-8.766200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0094</v>
+        <v>-6.496199999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.2855</v>
+        <v>4.9615</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2949</v>
+        <v>-11.4576</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9241</v>
+        <v>0.1016000000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5587</v>
+        <v>-2.5899</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4828</v>
+        <v>2.6915</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>4.8834</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1488</v>
+        <v>-15.6274</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>20.5109</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1673</v>
+        <v>-2.7924</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8441</v>
+        <v>3.7294</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3232</v>
+        <v>-6.5218</v>
       </c>
       <c r="V14" t="n">
-        <v>2.2149</v>
+        <v>-5.758100000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4373</v>
+        <v>2.0532</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2224</v>
-      </c>
+        <v>-7.811400000000001</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0096</v>
+        <v>4.6717</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0691</v>
+        <v>2.588</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0787</v>
+        <v>2.0837</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5741000000000001</v>
+        <v>3.1168</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5044999999999999</v>
+        <v>1.4183</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0786</v>
+        <v>1.6986</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7397</v>
+        <v>1.6631</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2008</v>
+        <v>1.5822</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5389</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3138</v>
+        <v>1.4537</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3036</v>
+        <v>-0.1639</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6174</v>
+        <v>1.6176</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>1.549</v>
+        <v>0.2228</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9329</v>
+        <v>0.3592</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6161</v>
+        <v>-0.1364</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8865</v>
+        <v>0.9414</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>2.7145</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2014</v>
+        <v>3.9249</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3571</v>
+        <v>1.1419</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8443</v>
+        <v>2.783</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5022</v>
+        <v>0.9335</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1276</v>
+        <v>-1.8442</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6299</v>
+        <v>2.7777</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9411</v>
+        <v>0.0094</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9849</v>
+        <v>-1.2855</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9562</v>
+        <v>1.2949</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4388</v>
+        <v>0.9241</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1125</v>
+        <v>-0.5587</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6737</v>
+        <v>1.4828</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.1673</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3461</v>
+        <v>0.8441</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6423</v>
+        <v>0.3232</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>2.2149</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0579</v>
+        <v>3.0096</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3227</v>
+        <v>-1.0691</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3807</v>
+        <v>4.0787</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.0297</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5899</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.4398</v>
+        <v>1.0786</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.9296</v>
+        <v>-0.7397</v>
       </c>
       <c r="K17" t="n">
-        <v>0.802</v>
+        <v>-0.2008</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.7315</v>
+        <v>-0.5389</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8998</v>
+        <v>1.3138</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3919</v>
+        <v>-0.3036</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2917</v>
+        <v>1.6174</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9301</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1928</v>
+        <v>1.549</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3649</v>
+        <v>0.9329</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8279</v>
+        <v>0.6161</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>0.8865</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5321</v>
+        <v>2.2014</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.3571</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1851</v>
+        <v>1.8443</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7529</v>
+        <v>2.5022</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8115</v>
+        <v>-0.1276</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5643</v>
+        <v>2.6299</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7027</v>
+        <v>2.9411</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.9849</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2949</v>
+        <v>1.9562</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0502</v>
+        <v>-0.4388</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2192</v>
+        <v>-1.1125</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2694</v>
+        <v>0.6737</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4161</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2098</v>
+        <v>0.3461</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.626</v>
+        <v>0.6423</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1977,72 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0439</v>
+        <v>2.0579</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8921</v>
+        <v>-2.3227</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8482</v>
+        <v>4.3807</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6458</v>
+        <v>-3.0297</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4743</v>
+        <v>-0.5899</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1715</v>
+        <v>-2.4398</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2521</v>
+        <v>-3.9296</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6984</v>
+        <v>0.802</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5537</v>
+        <v>-4.7315</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3938</v>
+        <v>0.8998</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2241</v>
+        <v>-1.3919</v>
       </c>
       <c r="O19" t="n">
-        <v>1.6178</v>
+        <v>2.2917</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.9069</v>
+        <v>1.9534</v>
       </c>
       <c r="Q19" t="n">
-        <v>-6.0556</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>2.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8302</v>
+        <v>2.1928</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9115</v>
+        <v>1.3649</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0813</v>
+        <v>0.8279</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3869</v>
+        <v>0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3869</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3629</v>
+        <v>1.5279</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7996</v>
+        <v>1.5279</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4367</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1009</v>
+        <v>1.5279</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3863</v>
+        <v>0.921</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7146</v>
+        <v>0.607</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0005</v>
+        <v>1.5279</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6011</v>
+        <v>0.921</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6016</v>
+        <v>0.607</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8997000000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9874000000000001</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.8871</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1873</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5534</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6339</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,318 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>0.5321</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7171999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.1851</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.8115</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.5643</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.5921999999999999</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.2949</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.2192</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.4161</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.626</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>J. GASCON TORNE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.8921</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.8482</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.6458</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.1715</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.2521</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.6984</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.5537</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.3938</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.2241</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.6178</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-6.0556</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.8302</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.0813</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>G. GARCIA RIERA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.8908</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-5.3275</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.4367</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.6288</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.3073</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.3216</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-3.5285</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.3198</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-3.2086</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.8997000000000001</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.9874000000000001</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.8871</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.1873</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.5534</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484369_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>15.9908</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E24" t="n">
         <v>-6.2793</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F24" t="n">
         <v>22.2702</v>
       </c>
-      <c r="G21" t="n">
-        <v>6.394699999999999</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G24" t="n">
+        <v>6.3947</v>
+      </c>
+      <c r="H24" t="n">
         <v>-2.3714</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I24" t="n">
         <v>8.7662</v>
       </c>
-      <c r="J21" t="n">
-        <v>-0.1014000000000004</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.5901</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-2.691399999999999</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.4963</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="J24" t="n">
+        <v>-0.1015000000000001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.5902</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2.6914</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6.496300000000001</v>
+      </c>
+      <c r="N24" t="n">
         <v>-4.9613</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O24" t="n">
         <v>11.4575</v>
       </c>
-      <c r="P21" t="n">
-        <v>-4.8837</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="P24" t="n">
+        <v>-4.883699999999999</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-20.511</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R24" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S24" t="n">
         <v>8.7217</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T24" t="n">
         <v>6.5219</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U24" t="n">
         <v>2.1997</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V24" t="n">
         <v>5.7581</v>
       </c>
-      <c r="W21" t="n">
-        <v>7.811399999999999</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="W24" t="n">
+        <v>7.8114</v>
+      </c>
+      <c r="X24" t="n">
         <v>-2.0533</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
